--- a/cds/mm_canada-5year-cds.xlsx
+++ b/cds/mm_canada-5year-cds.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="429">
   <si>
     <t>Date</t>
   </si>
@@ -1287,6 +1287,21 @@
   </si>
   <si>
     <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1651,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B423"/>
+  <dimension ref="A1:B428"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5021,6 +5036,46 @@
       </c>
       <c r="B423" s="3">
         <v>19.44</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B424" s="3">
+        <v>19.78</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B425" s="3">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B426" s="3">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B427" s="3">
+        <v>18.61</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B428" s="3">
+        <v>18.98</v>
       </c>
     </row>
   </sheetData>
